--- a/contest_registration_forms/037_short_story_contest_voting--contest_registration_forms.xlsx
+++ b/contest_registration_forms/037_short_story_contest_voting--contest_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -548,17 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Choose Your Story</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Select one story to vote for</t>
-        </is>
-      </c>
+          <t>Choose A Story</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -575,17 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Voting Type</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Select your vote type</t>
-        </is>
-      </c>
+          <t>Vote Type</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -602,30 +594,30 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>Rate the Story</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>Comment</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -643,156 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>submit_button</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Rating</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>rating</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Rating</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>submit_button</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>submit_button</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>submit_button</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Submit</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -807,12 +661,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -840,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>the_great_gatsby</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>The Great Gatsby</t>
         </is>
       </c>
     </row>
@@ -857,46 +711,80 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>the_catcher_in_the_rye</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>The Catcher in the Rye</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>vote_type_choices</t>
+          <t>story_choice_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>the_great_expectations</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>The Great Expectations</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>story_choice_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>the_old_man_and_the_sea</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>The Old Man and the Sea</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>vote_type_choices</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>No</t>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>for_the_win</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>For the win</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>vote_type_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>against_the_win</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Against the win</t>
         </is>
       </c>
     </row>
